--- a/reports/budget.xlsx
+++ b/reports/budget.xlsx
@@ -1,42 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29119"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/990c1ad3d5415923/1_Consulting/CAL FIRE Biz Devo/CAL FIRE Biz Devo Shared/Communications/auto-report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87D04074-4EBC-469A-B599-30B90CBB7AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{579D8B73-00E4-4960-8FA1-5E87DB3355D3}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Task</t>
   </si>
@@ -50,50 +30,71 @@
     <t>Remaining</t>
   </si>
   <si>
-    <t>1. Project planning</t>
-  </si>
-  <si>
-    <t>2. Implementation</t>
-  </si>
-  <si>
-    <t>3. Monitoring</t>
-  </si>
-  <si>
-    <t>4. Reporting</t>
-  </si>
-  <si>
-    <t>TOTALS</t>
+    <t xml:space="preserve">1. Project planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Implementation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1 Staffing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2 Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 Travel</t>
+  </si>
+  <si>
+    <t>sub-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1 Science review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2 Field collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Data analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Data viz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indirect (10%)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -105,39 +106,59 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -156,8 +177,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -199,108 +503,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Display"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -308,7 +518,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -334,7 +544,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -411,7 +621,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -443,7 +653,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -462,118 +672,272 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A362FA1-B407-4DF9-A717-D8B2867F07EC}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="20.8515625"/>
+    <col customWidth="1" min="2" max="2" width="12.33203125"/>
+    <col customWidth="1" min="3" max="3" width="11.6640625"/>
+    <col customWidth="1" min="4" max="4" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>20000</v>
       </c>
-      <c r="C2" s="2">
-        <v>15000</v>
-      </c>
-      <c r="D2" s="3">
-        <f>B2-C2</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2" s="4">
+        <v>15226</v>
+      </c>
+      <c r="D2" s="5">
+        <f t="shared" ref="D2:D6" si="0">B2-C2</f>
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
-        <v>150000</v>
-      </c>
-      <c r="C3" s="2">
-        <v>86499</v>
-      </c>
-      <c r="D3" s="3">
-        <f t="shared" ref="D3:D5" si="0">B3-C3</f>
-        <v>63501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="6">
+        <v>120000</v>
+      </c>
+      <c r="C4" s="6">
+        <v>74538</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>45462</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6">
+        <v>30000</v>
+      </c>
+      <c r="C5" s="6">
+        <v>12500</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6">
+        <v>40000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>9929</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>30071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4">
+        <f>SUM(B4:B6)</f>
+        <v>190000</v>
+      </c>
+      <c r="C7" s="4">
+        <f>SUM(C4:C6)</f>
+        <v>96967</v>
+      </c>
+      <c r="D7" s="5">
+        <f>SUM(D4:D6)</f>
+        <v>93033</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="6">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="7">
+        <f>B9-C9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6">
         <v>50000</v>
       </c>
-      <c r="C4" s="2">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="3">
-        <f t="shared" si="0"/>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="C10" s="6">
+        <v>25405</v>
+      </c>
+      <c r="D10" s="7">
+        <f>B10-C10</f>
+        <v>24595</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="6">
+        <v>75000</v>
+      </c>
+      <c r="C11" s="6">
+        <v>23232</v>
+      </c>
+      <c r="D11" s="7">
+        <f>B11-C11</f>
+        <v>51768</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6">
+        <v>90000</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7895</v>
+      </c>
+      <c r="D12" s="7">
+        <f>B12-C12</f>
+        <v>82105</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6">
+        <f>SUM(B8:B12)</f>
+        <v>220000</v>
+      </c>
+      <c r="C13" s="6">
+        <f>SUM(C8:C12)</f>
+        <v>61532</v>
+      </c>
+      <c r="D13" s="6">
+        <f>SUM(D8:D12)</f>
+        <v>158468</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6">
         <v>15000</v>
       </c>
-      <c r="C5" s="2">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="3">
-        <f t="shared" si="0"/>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4">
-        <f>SUM(B2:B5)</f>
-        <v>235000</v>
-      </c>
-      <c r="C6" s="4">
-        <f t="shared" ref="C6:D6" si="1">SUM(C2:C5)</f>
-        <v>113499</v>
-      </c>
-      <c r="D6" s="4">
-        <f t="shared" si="1"/>
-        <v>121501</v>
+      <c r="C14" s="6">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="6">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4">
+        <f>B14+B4+B7+B2</f>
+        <v>345000</v>
+      </c>
+      <c r="C15" s="4">
+        <f>C14+C8+C7+C2</f>
+        <v>127193</v>
+      </c>
+      <c r="D15" s="4">
+        <f>D14+D8+D7+D2</f>
+        <v>112807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B15*0.1</f>
+        <v>34500</v>
+      </c>
+      <c r="C16" s="6">
+        <f>C15*0.1</f>
+        <v>12719.300000000001</v>
+      </c>
+      <c r="D16" s="7">
+        <f>D15*0.1</f>
+        <v>11280.700000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="12">
+        <f>B16+B15</f>
+        <v>379500</v>
+      </c>
+      <c r="C17" s="12">
+        <f>C16+C15</f>
+        <v>139912.29999999999</v>
+      </c>
+      <c r="D17" s="12">
+        <f>D16+D15</f>
+        <v>124087.7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>